--- a/analysis/tables/ours-7b.xlsx
+++ b/analysis/tables/ours-7b.xlsx
@@ -495,30 +495,30 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5831687756605118</v>
+        <v>0.5833687986314176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03062941464382929</v>
+        <v>0.0304956546921597</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>y = 0.583x + 0.031</t>
+          <t>y = 0.583x + 0.030</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7838582598485035</v>
+        <v>0.7840719584357971</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08983128431400769</v>
+        <v>0.08982329992578182</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05252238446603667</v>
+        <v>-0.05227508698391561</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6137981903043411</v>
+        <v>0.6138644533235773</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2312223587223648</v>
+        <v>0.2312042320494592</v>
       </c>
     </row>
     <row r="3">
@@ -536,30 +536,30 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8682735314843862</v>
+        <v>0.9226664827582246</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05519846216489332</v>
+        <v>-0.2583900998488662</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.868x - 0.055</t>
+          <t>y = 0.923x - 0.258</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.847207712774909</v>
+        <v>0.8365716961611958</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08033063631815804</v>
+        <v>0.08027701071313023</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06357266479208105</v>
+        <v>0.2800471293553802</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8130750693194929</v>
+        <v>0.6642763829093584</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2312223587223648</v>
+        <v>0.2312042320494592</v>
       </c>
     </row>
     <row r="4">
@@ -577,30 +577,30 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8714038618269381</v>
+        <v>0.9121343742770236</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02225877082980504</v>
+        <v>-0.2447968741128076</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.871x - 0.022</t>
+          <t>y = 0.912x - 0.245</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8550880163505568</v>
+        <v>0.8390041846626251</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07996776824377196</v>
+        <v>0.08016392111852952</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02554357606717339</v>
+        <v>0.2683780822390764</v>
       </c>
       <c r="J4" t="n">
-        <v>0.849145090997133</v>
+        <v>0.667337500164216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2312223587223648</v>
+        <v>0.2312042320494592</v>
       </c>
     </row>
   </sheetData>
